--- a/Alberto_territory_chart.xlsx
+++ b/Alberto_territory_chart.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lesleyalberto\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CC6B4E9C-F433-4A5B-830C-6F629DC1D07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8E82DD78-696B-45EE-BC5E-B984C893F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{76AD1257-55AA-4FD8-B7F8-D67A7392BB64}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Line chart" sheetId="2" r:id="rId1"/>
     <sheet name="texas_revenue_monthly" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -604,7 +604,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Alberto_territory_chart.xlsx]Sheet1!PivotTable1</c:name>
+    <c:name>[Alberto_territory_chart.xlsx]Line chart!PivotTable1</c:name>
     <c:fmtId val="40"/>
   </c:pivotSource>
   <c:chart>
@@ -750,7 +750,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$3</c:f>
+              <c:f>'Line chart'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -790,7 +790,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$4:$A$16</c:f>
+              <c:f>'Line chart'!$A$4:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -834,7 +834,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$16</c:f>
+              <c:f>'Line chart'!$B$4:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1026,15 +1026,13 @@
       <a:schemeClr val="accent1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="accent1"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
   <c:txPr>
-    <a:bodyPr/>
+    <a:bodyPr anchor="t" anchorCtr="1"/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
